--- a/tests/discovery/fixtures/uruguay-location-seed.xlsx
+++ b/tests/discovery/fixtures/uruguay-location-seed.xlsx
@@ -1,47 +1,356 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <workbookPr codeName="ThisWorkbook"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet name="places" sheetId="1" r:id="rId1"/>
+    <sheet sheetId="1" name="places" state="visible" r:id="rId4"/>
   </sheets>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="109">
+  <si>
+    <t>location_key</t>
+  </si>
+  <si>
+    <t>display_name</t>
+  </si>
+  <si>
+    <t>parent_location</t>
+  </si>
+  <si>
+    <t>kind</t>
+  </si>
+  <si>
+    <t>lat_approx</t>
+  </si>
+  <si>
+    <t>lng_approx</t>
+  </si>
+  <si>
+    <t>commercial_score</t>
+  </si>
+  <si>
+    <t>notes</t>
+  </si>
+  <si>
+    <t>montevideo-departamento</t>
+  </si>
+  <si>
+    <t>Montevideo (Departamento)</t>
+  </si>
+  <si>
+    <t>departamento</t>
+  </si>
+  <si>
+    <t>SRC:IMM-MVD+OSM-MANUAL | Cabecera administrativa y mayor densidad comercial; centroide aproximado.</t>
+  </si>
+  <si>
+    <t>canelones-departamento</t>
+  </si>
+  <si>
+    <t>Canelones (Departamento)</t>
+  </si>
+  <si>
+    <t>SRC:IDC-CAN+OSM-MANUAL | Cabecera departamental y corredor metropolitano.</t>
+  </si>
+  <si>
+    <t>maldonado-departamento</t>
+  </si>
+  <si>
+    <t>Maldonado (Departamento)</t>
+  </si>
+  <si>
+    <t>SRC:IDM-MAL+MINTUR-UY+OSM-MANUAL | Principal corredor turistico-comercial del este.</t>
+  </si>
+  <si>
+    <t>rocha-departamento</t>
+  </si>
+  <si>
+    <t>Rocha (Departamento)</t>
+  </si>
+  <si>
+    <t>SRC:IDR-ROCHA+MINTUR-UY+OSM-MANUAL | Base costera para turismo de temporada.</t>
+  </si>
+  <si>
+    <t>salto-departamento</t>
+  </si>
+  <si>
+    <t>Salto (Departamento)</t>
+  </si>
+  <si>
+    <t>SRC:IDS-SALTO+MINTUR-UY+OSM-MANUAL | Nodo termal y comercial del litoral norte.</t>
+  </si>
+  <si>
+    <t>paysandu-departamento</t>
+  </si>
+  <si>
+    <t>Paysandu (Departamento)</t>
+  </si>
+  <si>
+    <t>SRC:IDP-PDU+OSM-MANUAL | Nodo comercial del litoral; centroide operativo ajustado al bound del validador.</t>
+  </si>
+  <si>
+    <t>colonia-departamento</t>
+  </si>
+  <si>
+    <t>Colonia (Departamento)</t>
+  </si>
+  <si>
+    <t>SRC:IDC-COL+MINTUR-UY+OSM-MANUAL | Eje turistico y logistico del suroeste.</t>
+  </si>
+  <si>
+    <t>montevideo</t>
+  </si>
+  <si>
+    <t>Montevideo</t>
+  </si>
+  <si>
+    <t>ciudad</t>
+  </si>
+  <si>
+    <t>SRC:IMM-MVD+OSM-MANUAL | Capital nacional; prioritaria para testing de filtros y score predictivo.</t>
+  </si>
+  <si>
+    <t>las-piedras</t>
+  </si>
+  <si>
+    <t>Las Piedras</t>
+  </si>
+  <si>
+    <t>SRC:IDC-CAN+OSM-MANUAL | Ciudad satelite con actividad retail y servicios.</t>
+  </si>
+  <si>
+    <t>punta-del-este</t>
+  </si>
+  <si>
+    <t>Punta del Este</t>
+  </si>
+  <si>
+    <t>SRC:IDM-MAL+MINTUR-UY+OSM-MANUAL | Polo turistico premium con alta senal comercial.</t>
+  </si>
+  <si>
+    <t>piriapolis</t>
+  </si>
+  <si>
+    <t>Piriapolis</t>
+  </si>
+  <si>
+    <t>SRC:IDM-MAL+MINTUR-UY+OSM-MANUAL | Ciudad balnearia con temporada extendida.</t>
+  </si>
+  <si>
+    <t>rocha</t>
+  </si>
+  <si>
+    <t>Rocha</t>
+  </si>
+  <si>
+    <t>SRC:IDR-ROCHA+OSM-MANUAL | Capital departamental de soporte para costa este.</t>
+  </si>
+  <si>
+    <t>la-paloma</t>
+  </si>
+  <si>
+    <t>La Paloma</t>
+  </si>
+  <si>
+    <t>SRC:IDR-ROCHA+MINTUR-UY+OSM-MANUAL | Balneario con frente comercial y gastronomico.</t>
+  </si>
+  <si>
+    <t>salto</t>
+  </si>
+  <si>
+    <t>Salto</t>
+  </si>
+  <si>
+    <t>SRC:IDS-SALTO+OSM-MANUAL | Capital departamental y puerta a circuitos termales.</t>
+  </si>
+  <si>
+    <t>paysandu</t>
+  </si>
+  <si>
+    <t>Paysandu</t>
+  </si>
+  <si>
+    <t>SRC:IDP-PDU+OSM-MANUAL | Capital departamental con avenida comercial consolidada.</t>
+  </si>
+  <si>
+    <t>colonia-del-sacramento</t>
+  </si>
+  <si>
+    <t>Colonia del Sacramento</t>
+  </si>
+  <si>
+    <t>SRC:IDC-COL+MINTUR-UY+OSM-MANUAL | Ciudad historica y turistica con comercio orientado a visitantes.</t>
+  </si>
+  <si>
+    <t>ciudad-vieja-mvd</t>
+  </si>
+  <si>
+    <t>Ciudad Vieja</t>
+  </si>
+  <si>
+    <t>barrio</t>
+  </si>
+  <si>
+    <t>SRC:IMM-MVD+OSM-MANUAL | Barrio historico con gastronomia, turismo y oficinas.</t>
+  </si>
+  <si>
+    <t>centro-mvd</t>
+  </si>
+  <si>
+    <t>Centro</t>
+  </si>
+  <si>
+    <t>SRC:IMM-MVD+OSM-MANUAL | Centralidad comercial de alto flujo peatonal.</t>
+  </si>
+  <si>
+    <t>cordon-mvd</t>
+  </si>
+  <si>
+    <t>Cordon</t>
+  </si>
+  <si>
+    <t>SRC:IMM-MVD+OSM-MANUAL | Mezcla de servicios, educacion y gastronomia.</t>
+  </si>
+  <si>
+    <t>pocitos-mvd</t>
+  </si>
+  <si>
+    <t>Pocitos</t>
+  </si>
+  <si>
+    <t>SRC:IMM-MVD+OSM-MANUAL | Barrio denso en retail, gastronomia y salud privada.</t>
+  </si>
+  <si>
+    <t>punta-carretas-mvd</t>
+  </si>
+  <si>
+    <t>Punta Carretas</t>
+  </si>
+  <si>
+    <t>SRC:IMM-MVD+OSM-MANUAL | Zona comercial premium y de oficinas.</t>
+  </si>
+  <si>
+    <t>carrasco-mvd</t>
+  </si>
+  <si>
+    <t>Carrasco</t>
+  </si>
+  <si>
+    <t>SRC:IMM-MVD+OSM-MANUAL | Corredor gastronomico y servicios de ticket alto.</t>
+  </si>
+  <si>
+    <t>avenida-18-de-julio</t>
+  </si>
+  <si>
+    <t>Av. 18 de Julio</t>
+  </si>
+  <si>
+    <t>avenida</t>
+  </si>
+  <si>
+    <t>SRC:IMM-MVD+OSM-MANUAL | Avenida comercial troncal para filtros por centralidad.</t>
+  </si>
+  <si>
+    <t>peninsula-pde</t>
+  </si>
+  <si>
+    <t>Peninsula</t>
+  </si>
+  <si>
+    <t>zona_turistica</t>
+  </si>
+  <si>
+    <t>SRC:IDM-MAL+MINTUR-UY+OSM-MANUAL | Nucleo turistico y gastronomico de alta estacionalidad.</t>
+  </si>
+  <si>
+    <t>avenida-gorlero</t>
+  </si>
+  <si>
+    <t>Av. Gorlero</t>
+  </si>
+  <si>
+    <t>SRC:IDM-MAL+OSM-MANUAL | Eje comercial iconico del balneario.</t>
+  </si>
+  <si>
+    <t>puerto-pde</t>
+  </si>
+  <si>
+    <t>Puerto de Punta del Este</t>
+  </si>
+  <si>
+    <t>SRC:IDM-MAL+MINTUR-UY+OSM-MANUAL | Gastronomia y turismo nautico.</t>
+  </si>
+  <si>
+    <t>la-barra</t>
+  </si>
+  <si>
+    <t>La Barra</t>
+  </si>
+  <si>
+    <t>SRC:IDM-MAL+MINTUR-UY+OSM-MANUAL | Corredor de temporada con retail y ocio.</t>
+  </si>
+  <si>
+    <t>barrio-historico-colonia</t>
+  </si>
+  <si>
+    <t>Barrio Historico</t>
+  </si>
+  <si>
+    <t>SRC:IDC-COL+MINTUR-UY+OSM-MANUAL | Cluster turistico y gastronomico UNESCO.</t>
+  </si>
+  <si>
+    <t>termas-del-dayman</t>
+  </si>
+  <si>
+    <t>Termas del Dayman</t>
+  </si>
+  <si>
+    <t>SRC:IDS-SALTO+MINTUR-UY+OSM-MANUAL | Circuito termal con hoteleria y servicios.</t>
+  </si>
+  <si>
+    <t>rambla-de-los-argentinos</t>
+  </si>
+  <si>
+    <t>Rambla de los Argentinos</t>
+  </si>
+  <si>
+    <t>SRC:IDM-MAL+OSM-MANUAL | Frente costero comercial y gastronomico.</t>
+  </si>
+  <si>
+    <t>puerto-la-paloma</t>
+  </si>
+  <si>
+    <t>Puerto de La Paloma</t>
+  </si>
+  <si>
+    <t>SRC:IDR-ROCHA+MINTUR-UY+OSM-MANUAL | Gastronomia y pesca/turismo costero.</t>
+  </si>
+  <si>
+    <t>avenida-espana-paysandu</t>
+  </si>
+  <si>
+    <t>Av. Espana</t>
+  </si>
+  <si>
+    <t>SRC:IDP-PDU+OSM-MANUAL | Corredor urbano operativo para pruebas en el litoral.</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
-      <sz val="12"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
@@ -65,13 +374,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -396,44 +713,45 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H33"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>location_key</v>
-      </c>
-      <c r="B1" t="str">
-        <v>display_name</v>
-      </c>
-      <c r="C1" t="str">
-        <v>parent_location</v>
-      </c>
-      <c r="D1" t="str">
-        <v>kind</v>
-      </c>
-      <c r="E1" t="str">
-        <v>lat_approx</v>
-      </c>
-      <c r="F1" t="str">
-        <v>lng_approx</v>
-      </c>
-      <c r="G1" t="str">
-        <v>commercial_score</v>
-      </c>
-      <c r="H1" t="str">
-        <v>notes</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>montevideo-departamento</v>
-      </c>
-      <c r="B2" t="str">
-        <v>Montevideo (Departamento)</v>
-      </c>
-      <c r="D2" t="str">
-        <v>departamento</v>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" t="s">
+        <v>10</v>
       </c>
       <c r="E2">
         <v>-34.9011</v>
@@ -444,19 +762,19 @@
       <c r="G2">
         <v>95</v>
       </c>
-      <c r="H2" t="str">
-        <v>SRC:IMM-MVD+OSM-MANUAL | Cabecera administrativa y mayor densidad comercial; centroide aproximado.</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>canelones-departamento</v>
-      </c>
-      <c r="B3" t="str">
-        <v>Canelones (Departamento)</v>
-      </c>
-      <c r="D3" t="str">
-        <v>departamento</v>
+      <c r="H2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" t="s">
+        <v>10</v>
       </c>
       <c r="E3">
         <v>-34.5228</v>
@@ -467,19 +785,19 @@
       <c r="G3">
         <v>78</v>
       </c>
-      <c r="H3" t="str">
-        <v>SRC:IDC-CAN+OSM-MANUAL | Cabecera departamental y corredor metropolitano.</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>maldonado-departamento</v>
-      </c>
-      <c r="B4" t="str">
-        <v>Maldonado (Departamento)</v>
-      </c>
-      <c r="D4" t="str">
-        <v>departamento</v>
+      <c r="H3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" t="s">
+        <v>10</v>
       </c>
       <c r="E4">
         <v>-34.9</v>
@@ -490,19 +808,19 @@
       <c r="G4">
         <v>90</v>
       </c>
-      <c r="H4" t="str">
-        <v>SRC:IDM-MAL+MINTUR-UY+OSM-MANUAL | Principal corredor turistico-comercial del este.</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>rocha-departamento</v>
-      </c>
-      <c r="B5" t="str">
-        <v>Rocha (Departamento)</v>
-      </c>
-      <c r="D5" t="str">
-        <v>departamento</v>
+      <c r="H4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5" t="s">
+        <v>10</v>
       </c>
       <c r="E5">
         <v>-34.4833</v>
@@ -513,19 +831,19 @@
       <c r="G5">
         <v>70</v>
       </c>
-      <c r="H5" t="str">
-        <v>SRC:IDR-ROCHA+MINTUR-UY+OSM-MANUAL | Base costera para turismo de temporada.</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>salto-departamento</v>
-      </c>
-      <c r="B6" t="str">
-        <v>Salto (Departamento)</v>
-      </c>
-      <c r="D6" t="str">
-        <v>departamento</v>
+      <c r="H5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" t="s">
+        <v>10</v>
       </c>
       <c r="E6">
         <v>-31.3833</v>
@@ -536,19 +854,19 @@
       <c r="G6">
         <v>76</v>
       </c>
-      <c r="H6" t="str">
-        <v>SRC:IDS-SALTO+MINTUR-UY+OSM-MANUAL | Nodo termal y comercial del litoral norte.</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>paysandu-departamento</v>
-      </c>
-      <c r="B7" t="str">
-        <v>Paysandu (Departamento)</v>
-      </c>
-      <c r="D7" t="str">
-        <v>departamento</v>
+      <c r="H6" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" t="s">
+        <v>25</v>
+      </c>
+      <c r="D7" t="s">
+        <v>10</v>
       </c>
       <c r="E7">
         <v>-32.3214</v>
@@ -559,19 +877,19 @@
       <c r="G7">
         <v>73</v>
       </c>
-      <c r="H7" t="str">
-        <v>SRC:IDP-PDU+OSM-MANUAL | Nodo comercial del litoral; centroide operativo ajustado al bound del validador.</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>colonia-departamento</v>
-      </c>
-      <c r="B8" t="str">
-        <v>Colonia (Departamento)</v>
-      </c>
-      <c r="D8" t="str">
-        <v>departamento</v>
+      <c r="H7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>27</v>
+      </c>
+      <c r="B8" t="s">
+        <v>28</v>
+      </c>
+      <c r="D8" t="s">
+        <v>10</v>
       </c>
       <c r="E8">
         <v>-34.2</v>
@@ -582,22 +900,22 @@
       <c r="G8">
         <v>74</v>
       </c>
-      <c r="H8" t="str">
-        <v>SRC:IDC-COL+MINTUR-UY+OSM-MANUAL | Eje turistico y logistico del suroeste.</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>montevideo</v>
-      </c>
-      <c r="B9" t="str">
-        <v>Montevideo</v>
-      </c>
-      <c r="C9" t="str">
-        <v>Montevideo (Departamento)</v>
-      </c>
-      <c r="D9" t="str">
-        <v>ciudad</v>
+      <c r="H8" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>30</v>
+      </c>
+      <c r="B9" t="s">
+        <v>31</v>
+      </c>
+      <c r="C9" t="s">
+        <v>9</v>
+      </c>
+      <c r="D9" t="s">
+        <v>32</v>
       </c>
       <c r="E9">
         <v>-34.9011</v>
@@ -608,22 +926,22 @@
       <c r="G9">
         <v>96</v>
       </c>
-      <c r="H9" t="str">
-        <v>SRC:IMM-MVD+OSM-MANUAL | Capital nacional; prioritaria para testing de filtros y score predictivo.</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>las-piedras</v>
-      </c>
-      <c r="B10" t="str">
-        <v>Las Piedras</v>
-      </c>
-      <c r="C10" t="str">
-        <v>Canelones (Departamento)</v>
-      </c>
-      <c r="D10" t="str">
-        <v>ciudad</v>
+      <c r="H9" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>34</v>
+      </c>
+      <c r="B10" t="s">
+        <v>35</v>
+      </c>
+      <c r="C10" t="s">
+        <v>13</v>
+      </c>
+      <c r="D10" t="s">
+        <v>32</v>
       </c>
       <c r="E10">
         <v>-34.73</v>
@@ -634,22 +952,22 @@
       <c r="G10">
         <v>68</v>
       </c>
-      <c r="H10" t="str">
-        <v>SRC:IDC-CAN+OSM-MANUAL | Ciudad satelite con actividad retail y servicios.</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>punta-del-este</v>
-      </c>
-      <c r="B11" t="str">
-        <v>Punta del Este</v>
-      </c>
-      <c r="C11" t="str">
-        <v>Maldonado (Departamento)</v>
-      </c>
-      <c r="D11" t="str">
-        <v>ciudad</v>
+      <c r="H10" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>37</v>
+      </c>
+      <c r="B11" t="s">
+        <v>38</v>
+      </c>
+      <c r="C11" t="s">
+        <v>16</v>
+      </c>
+      <c r="D11" t="s">
+        <v>32</v>
       </c>
       <c r="E11">
         <v>-34.96</v>
@@ -660,22 +978,22 @@
       <c r="G11">
         <v>94</v>
       </c>
-      <c r="H11" t="str">
-        <v>SRC:IDM-MAL+MINTUR-UY+OSM-MANUAL | Polo turistico premium con alta senal comercial.</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>piriapolis</v>
-      </c>
-      <c r="B12" t="str">
-        <v>Piriapolis</v>
-      </c>
-      <c r="C12" t="str">
-        <v>Maldonado (Departamento)</v>
-      </c>
-      <c r="D12" t="str">
-        <v>ciudad</v>
+      <c r="H11" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>40</v>
+      </c>
+      <c r="B12" t="s">
+        <v>41</v>
+      </c>
+      <c r="C12" t="s">
+        <v>16</v>
+      </c>
+      <c r="D12" t="s">
+        <v>32</v>
       </c>
       <c r="E12">
         <v>-34.862</v>
@@ -686,22 +1004,22 @@
       <c r="G12">
         <v>83</v>
       </c>
-      <c r="H12" t="str">
-        <v>SRC:IDM-MAL+MINTUR-UY+OSM-MANUAL | Ciudad balnearia con temporada extendida.</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>rocha</v>
-      </c>
-      <c r="B13" t="str">
-        <v>Rocha</v>
-      </c>
-      <c r="C13" t="str">
-        <v>Rocha (Departamento)</v>
-      </c>
-      <c r="D13" t="str">
-        <v>ciudad</v>
+      <c r="H12" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B13" t="s">
+        <v>44</v>
+      </c>
+      <c r="C13" t="s">
+        <v>19</v>
+      </c>
+      <c r="D13" t="s">
+        <v>32</v>
       </c>
       <c r="E13">
         <v>-34.483</v>
@@ -712,22 +1030,22 @@
       <c r="G13">
         <v>66</v>
       </c>
-      <c r="H13" t="str">
-        <v>SRC:IDR-ROCHA+OSM-MANUAL | Capital departamental de soporte para costa este.</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>la-paloma</v>
-      </c>
-      <c r="B14" t="str">
-        <v>La Paloma</v>
-      </c>
-      <c r="C14" t="str">
-        <v>Rocha (Departamento)</v>
-      </c>
-      <c r="D14" t="str">
-        <v>ciudad</v>
+      <c r="H13" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>46</v>
+      </c>
+      <c r="B14" t="s">
+        <v>47</v>
+      </c>
+      <c r="C14" t="s">
+        <v>19</v>
+      </c>
+      <c r="D14" t="s">
+        <v>32</v>
       </c>
       <c r="E14">
         <v>-34.662</v>
@@ -738,22 +1056,22 @@
       <c r="G14">
         <v>79</v>
       </c>
-      <c r="H14" t="str">
-        <v>SRC:IDR-ROCHA+MINTUR-UY+OSM-MANUAL | Balneario con frente comercial y gastronomico.</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>salto</v>
-      </c>
-      <c r="B15" t="str">
-        <v>Salto</v>
-      </c>
-      <c r="C15" t="str">
-        <v>Salto (Departamento)</v>
-      </c>
-      <c r="D15" t="str">
-        <v>ciudad</v>
+      <c r="H14" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>49</v>
+      </c>
+      <c r="B15" t="s">
+        <v>50</v>
+      </c>
+      <c r="C15" t="s">
+        <v>22</v>
+      </c>
+      <c r="D15" t="s">
+        <v>32</v>
       </c>
       <c r="E15">
         <v>-31.39</v>
@@ -764,22 +1082,22 @@
       <c r="G15">
         <v>82</v>
       </c>
-      <c r="H15" t="str">
-        <v>SRC:IDS-SALTO+OSM-MANUAL | Capital departamental y puerta a circuitos termales.</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>paysandu</v>
-      </c>
-      <c r="B16" t="str">
-        <v>Paysandu</v>
-      </c>
-      <c r="C16" t="str">
-        <v>Paysandu (Departamento)</v>
-      </c>
-      <c r="D16" t="str">
-        <v>ciudad</v>
+      <c r="H15" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>52</v>
+      </c>
+      <c r="B16" t="s">
+        <v>53</v>
+      </c>
+      <c r="C16" t="s">
+        <v>25</v>
+      </c>
+      <c r="D16" t="s">
+        <v>32</v>
       </c>
       <c r="E16">
         <v>-32.32</v>
@@ -790,22 +1108,22 @@
       <c r="G16">
         <v>78</v>
       </c>
-      <c r="H16" t="str">
-        <v>SRC:IDP-PDU+OSM-MANUAL | Capital departamental con avenida comercial consolidada.</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="str">
-        <v>colonia-del-sacramento</v>
-      </c>
-      <c r="B17" t="str">
-        <v>Colonia del Sacramento</v>
-      </c>
-      <c r="C17" t="str">
-        <v>Colonia (Departamento)</v>
-      </c>
-      <c r="D17" t="str">
-        <v>ciudad</v>
+      <c r="H16" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>55</v>
+      </c>
+      <c r="B17" t="s">
+        <v>56</v>
+      </c>
+      <c r="C17" t="s">
+        <v>28</v>
+      </c>
+      <c r="D17" t="s">
+        <v>32</v>
       </c>
       <c r="E17">
         <v>-34.471</v>
@@ -816,22 +1134,22 @@
       <c r="G17">
         <v>84</v>
       </c>
-      <c r="H17" t="str">
-        <v>SRC:IDC-COL+MINTUR-UY+OSM-MANUAL | Ciudad historica y turistica con comercio orientado a visitantes.</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="str">
-        <v>ciudad-vieja-mvd</v>
-      </c>
-      <c r="B18" t="str">
-        <v>Ciudad Vieja</v>
-      </c>
-      <c r="C18" t="str">
-        <v>Montevideo</v>
-      </c>
-      <c r="D18" t="str">
-        <v>barrio</v>
+      <c r="H17" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>58</v>
+      </c>
+      <c r="B18" t="s">
+        <v>59</v>
+      </c>
+      <c r="C18" t="s">
+        <v>31</v>
+      </c>
+      <c r="D18" t="s">
+        <v>60</v>
       </c>
       <c r="E18">
         <v>-34.907</v>
@@ -842,22 +1160,22 @@
       <c r="G18">
         <v>88</v>
       </c>
-      <c r="H18" t="str">
-        <v>SRC:IMM-MVD+OSM-MANUAL | Barrio historico con gastronomia, turismo y oficinas.</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="str">
-        <v>centro-mvd</v>
-      </c>
-      <c r="B19" t="str">
-        <v>Centro</v>
-      </c>
-      <c r="C19" t="str">
-        <v>Montevideo</v>
-      </c>
-      <c r="D19" t="str">
-        <v>barrio</v>
+      <c r="H18" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>62</v>
+      </c>
+      <c r="B19" t="s">
+        <v>63</v>
+      </c>
+      <c r="C19" t="s">
+        <v>31</v>
+      </c>
+      <c r="D19" t="s">
+        <v>60</v>
       </c>
       <c r="E19">
         <v>-34.905</v>
@@ -868,22 +1186,22 @@
       <c r="G19">
         <v>91</v>
       </c>
-      <c r="H19" t="str">
-        <v>SRC:IMM-MVD+OSM-MANUAL | Centralidad comercial de alto flujo peatonal.</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="str">
-        <v>cordon-mvd</v>
-      </c>
-      <c r="B20" t="str">
-        <v>Cordon</v>
-      </c>
-      <c r="C20" t="str">
-        <v>Montevideo</v>
-      </c>
-      <c r="D20" t="str">
-        <v>barrio</v>
+      <c r="H19" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>65</v>
+      </c>
+      <c r="B20" t="s">
+        <v>66</v>
+      </c>
+      <c r="C20" t="s">
+        <v>31</v>
+      </c>
+      <c r="D20" t="s">
+        <v>60</v>
       </c>
       <c r="E20">
         <v>-34.902</v>
@@ -894,22 +1212,22 @@
       <c r="G20">
         <v>87</v>
       </c>
-      <c r="H20" t="str">
-        <v>SRC:IMM-MVD+OSM-MANUAL | Mezcla de servicios, educacion y gastronomia.</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="str">
-        <v>pocitos-mvd</v>
-      </c>
-      <c r="B21" t="str">
-        <v>Pocitos</v>
-      </c>
-      <c r="C21" t="str">
-        <v>Montevideo</v>
-      </c>
-      <c r="D21" t="str">
-        <v>barrio</v>
+      <c r="H20" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>68</v>
+      </c>
+      <c r="B21" t="s">
+        <v>69</v>
+      </c>
+      <c r="C21" t="s">
+        <v>31</v>
+      </c>
+      <c r="D21" t="s">
+        <v>60</v>
       </c>
       <c r="E21">
         <v>-34.916</v>
@@ -920,22 +1238,22 @@
       <c r="G21">
         <v>93</v>
       </c>
-      <c r="H21" t="str">
-        <v>SRC:IMM-MVD+OSM-MANUAL | Barrio denso en retail, gastronomia y salud privada.</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="str">
-        <v>punta-carretas-mvd</v>
-      </c>
-      <c r="B22" t="str">
-        <v>Punta Carretas</v>
-      </c>
-      <c r="C22" t="str">
-        <v>Montevideo</v>
-      </c>
-      <c r="D22" t="str">
-        <v>barrio</v>
+      <c r="H21" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>71</v>
+      </c>
+      <c r="B22" t="s">
+        <v>72</v>
+      </c>
+      <c r="C22" t="s">
+        <v>31</v>
+      </c>
+      <c r="D22" t="s">
+        <v>60</v>
       </c>
       <c r="E22">
         <v>-34.923</v>
@@ -946,22 +1264,22 @@
       <c r="G22">
         <v>89</v>
       </c>
-      <c r="H22" t="str">
-        <v>SRC:IMM-MVD+OSM-MANUAL | Zona comercial premium y de oficinas.</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="str">
-        <v>carrasco-mvd</v>
-      </c>
-      <c r="B23" t="str">
-        <v>Carrasco</v>
-      </c>
-      <c r="C23" t="str">
-        <v>Montevideo</v>
-      </c>
-      <c r="D23" t="str">
-        <v>barrio</v>
+      <c r="H22" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>74</v>
+      </c>
+      <c r="B23" t="s">
+        <v>75</v>
+      </c>
+      <c r="C23" t="s">
+        <v>31</v>
+      </c>
+      <c r="D23" t="s">
+        <v>60</v>
       </c>
       <c r="E23">
         <v>-34.885</v>
@@ -972,22 +1290,22 @@
       <c r="G23">
         <v>86</v>
       </c>
-      <c r="H23" t="str">
-        <v>SRC:IMM-MVD+OSM-MANUAL | Corredor gastronomico y servicios de ticket alto.</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="str">
-        <v>avenida-18-de-julio</v>
-      </c>
-      <c r="B24" t="str">
-        <v>Av. 18 de Julio</v>
-      </c>
-      <c r="C24" t="str">
-        <v>Montevideo</v>
-      </c>
-      <c r="D24" t="str">
-        <v>avenida</v>
+      <c r="H23" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>77</v>
+      </c>
+      <c r="B24" t="s">
+        <v>78</v>
+      </c>
+      <c r="C24" t="s">
+        <v>31</v>
+      </c>
+      <c r="D24" t="s">
+        <v>79</v>
       </c>
       <c r="E24">
         <v>-34.905</v>
@@ -998,22 +1316,22 @@
       <c r="G24">
         <v>90</v>
       </c>
-      <c r="H24" t="str">
-        <v>SRC:IMM-MVD+OSM-MANUAL | Avenida comercial troncal para filtros por centralidad.</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="str">
-        <v>peninsula-pde</v>
-      </c>
-      <c r="B25" t="str">
-        <v>Peninsula</v>
-      </c>
-      <c r="C25" t="str">
-        <v>Punta del Este</v>
-      </c>
-      <c r="D25" t="str">
-        <v>zona_turistica</v>
+      <c r="H24" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>81</v>
+      </c>
+      <c r="B25" t="s">
+        <v>82</v>
+      </c>
+      <c r="C25" t="s">
+        <v>38</v>
+      </c>
+      <c r="D25" t="s">
+        <v>83</v>
       </c>
       <c r="E25">
         <v>-34.968</v>
@@ -1024,22 +1342,22 @@
       <c r="G25">
         <v>95</v>
       </c>
-      <c r="H25" t="str">
-        <v>SRC:IDM-MAL+MINTUR-UY+OSM-MANUAL | Nucleo turistico y gastronomico de alta estacionalidad.</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="str">
-        <v>avenida-gorlero</v>
-      </c>
-      <c r="B26" t="str">
-        <v>Av. Gorlero</v>
-      </c>
-      <c r="C26" t="str">
-        <v>Punta del Este</v>
-      </c>
-      <c r="D26" t="str">
-        <v>avenida</v>
+      <c r="H25" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>85</v>
+      </c>
+      <c r="B26" t="s">
+        <v>86</v>
+      </c>
+      <c r="C26" t="s">
+        <v>38</v>
+      </c>
+      <c r="D26" t="s">
+        <v>79</v>
       </c>
       <c r="E26">
         <v>-34.961</v>
@@ -1050,22 +1368,22 @@
       <c r="G26">
         <v>89</v>
       </c>
-      <c r="H26" t="str">
-        <v>SRC:IDM-MAL+OSM-MANUAL | Eje comercial iconico del balneario.</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="str">
-        <v>puerto-pde</v>
-      </c>
-      <c r="B27" t="str">
-        <v>Puerto de Punta del Este</v>
-      </c>
-      <c r="C27" t="str">
-        <v>Punta del Este</v>
-      </c>
-      <c r="D27" t="str">
-        <v>zona_turistica</v>
+      <c r="H26" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>88</v>
+      </c>
+      <c r="B27" t="s">
+        <v>89</v>
+      </c>
+      <c r="C27" t="s">
+        <v>38</v>
+      </c>
+      <c r="D27" t="s">
+        <v>83</v>
       </c>
       <c r="E27">
         <v>-34.967</v>
@@ -1076,22 +1394,22 @@
       <c r="G27">
         <v>88</v>
       </c>
-      <c r="H27" t="str">
-        <v>SRC:IDM-MAL+MINTUR-UY+OSM-MANUAL | Gastronomia y turismo nautico.</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="str">
-        <v>la-barra</v>
-      </c>
-      <c r="B28" t="str">
-        <v>La Barra</v>
-      </c>
-      <c r="C28" t="str">
-        <v>Punta del Este</v>
-      </c>
-      <c r="D28" t="str">
-        <v>zona_turistica</v>
+      <c r="H27" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>91</v>
+      </c>
+      <c r="B28" t="s">
+        <v>92</v>
+      </c>
+      <c r="C28" t="s">
+        <v>38</v>
+      </c>
+      <c r="D28" t="s">
+        <v>83</v>
       </c>
       <c r="E28">
         <v>-34.918</v>
@@ -1102,22 +1420,22 @@
       <c r="G28">
         <v>81</v>
       </c>
-      <c r="H28" t="str">
-        <v>SRC:IDM-MAL+MINTUR-UY+OSM-MANUAL | Corredor de temporada con retail y ocio.</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="str">
-        <v>barrio-historico-colonia</v>
-      </c>
-      <c r="B29" t="str">
-        <v>Barrio Historico</v>
-      </c>
-      <c r="C29" t="str">
-        <v>Colonia del Sacramento</v>
-      </c>
-      <c r="D29" t="str">
-        <v>zona_turistica</v>
+      <c r="H28" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>94</v>
+      </c>
+      <c r="B29" t="s">
+        <v>95</v>
+      </c>
+      <c r="C29" t="s">
+        <v>56</v>
+      </c>
+      <c r="D29" t="s">
+        <v>83</v>
       </c>
       <c r="E29">
         <v>-34.471</v>
@@ -1128,22 +1446,22 @@
       <c r="G29">
         <v>90</v>
       </c>
-      <c r="H29" t="str">
-        <v>SRC:IDC-COL+MINTUR-UY+OSM-MANUAL | Cluster turistico y gastronomico UNESCO.</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="str">
-        <v>termas-del-dayman</v>
-      </c>
-      <c r="B30" t="str">
-        <v>Termas del Dayman</v>
-      </c>
-      <c r="C30" t="str">
-        <v>Salto</v>
-      </c>
-      <c r="D30" t="str">
-        <v>zona_turistica</v>
+      <c r="H29" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>97</v>
+      </c>
+      <c r="B30" t="s">
+        <v>98</v>
+      </c>
+      <c r="C30" t="s">
+        <v>50</v>
+      </c>
+      <c r="D30" t="s">
+        <v>83</v>
       </c>
       <c r="E30">
         <v>-31.49</v>
@@ -1154,22 +1472,22 @@
       <c r="G30">
         <v>77</v>
       </c>
-      <c r="H30" t="str">
-        <v>SRC:IDS-SALTO+MINTUR-UY+OSM-MANUAL | Circuito termal con hoteleria y servicios.</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="str">
-        <v>rambla-de-los-argentinos</v>
-      </c>
-      <c r="B31" t="str">
-        <v>Rambla de los Argentinos</v>
-      </c>
-      <c r="C31" t="str">
-        <v>Piriapolis</v>
-      </c>
-      <c r="D31" t="str">
-        <v>avenida</v>
+      <c r="H30" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>100</v>
+      </c>
+      <c r="B31" t="s">
+        <v>101</v>
+      </c>
+      <c r="C31" t="s">
+        <v>41</v>
+      </c>
+      <c r="D31" t="s">
+        <v>79</v>
       </c>
       <c r="E31">
         <v>-34.863</v>
@@ -1180,22 +1498,22 @@
       <c r="G31">
         <v>78</v>
       </c>
-      <c r="H31" t="str">
-        <v>SRC:IDM-MAL+OSM-MANUAL | Frente costero comercial y gastronomico.</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="str">
-        <v>puerto-la-paloma</v>
-      </c>
-      <c r="B32" t="str">
-        <v>Puerto de La Paloma</v>
-      </c>
-      <c r="C32" t="str">
-        <v>La Paloma</v>
-      </c>
-      <c r="D32" t="str">
-        <v>zona_turistica</v>
+      <c r="H31" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>103</v>
+      </c>
+      <c r="B32" t="s">
+        <v>104</v>
+      </c>
+      <c r="C32" t="s">
+        <v>47</v>
+      </c>
+      <c r="D32" t="s">
+        <v>83</v>
       </c>
       <c r="E32">
         <v>-34.662</v>
@@ -1206,22 +1524,22 @@
       <c r="G32">
         <v>76</v>
       </c>
-      <c r="H32" t="str">
-        <v>SRC:IDR-ROCHA+MINTUR-UY+OSM-MANUAL | Gastronomia y pesca/turismo costero.</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="str">
-        <v>avenida-espana-paysandu</v>
-      </c>
-      <c r="B33" t="str">
-        <v>Av. Espana</v>
-      </c>
-      <c r="C33" t="str">
-        <v>Paysandu</v>
-      </c>
-      <c r="D33" t="str">
-        <v>avenida</v>
+      <c r="H32" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>106</v>
+      </c>
+      <c r="B33" t="s">
+        <v>107</v>
+      </c>
+      <c r="C33" t="s">
+        <v>53</v>
+      </c>
+      <c r="D33" t="s">
+        <v>79</v>
       </c>
       <c r="E33">
         <v>-32.321</v>
@@ -1232,13 +1550,12 @@
       <c r="G33">
         <v>71</v>
       </c>
-      <c r="H33" t="str">
-        <v>SRC:IDP-PDU+OSM-MANUAL | Corredor urbano operativo para pruebas en el litoral.</v>
+      <c r="H33" t="s">
+        <v>108</v>
       </c>
     </row>
   </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H33"/>
-  </ignoredErrors>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>